--- a/rule_analysis_report.xlsx
+++ b/rule_analysis_report.xlsx
@@ -664,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -949,98 +949,50 @@
     <row r="7" ht="72" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>invalid_enum</t>
+          <t>semantic_probe</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>enum 목록에 정의된 값 외의 값 전송 시 API가 오류를 반환하는지 검증.</t>
+          <t>semantic tag 기반으로 도메인 의미 규칙 위반값 주입. base64 포맷 오류, 빈값, 극단값 등.</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>enum 타입 파라미터/필드에 허용 목록 외 값 주입</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>domain</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>must_fail</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>success=false AND error_code&lt;0</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>success=true 반환 (enum 무시)
-5xx crash</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>domain.enum_violation</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>enum 항목 외 대표값 1~2개 TC 생성</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="72" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>semantic_probe</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>semantic tag 기반으로 도메인 의미 규칙 위반값 주입. base64 포맷 오류, 빈값, 극단값 등.</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>semantic_tag 지정 파라미터에 대해 _SEMANTIC_PROBES 정의 기반 값 주입
 (invalid_b64, empty_b64, range_probe 등)</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>tag별 상이
 (must_fail / probe_only)</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>must_fail: success=false, error_code&lt;0
 probe_only: status &lt; 500</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>must_fail: success=true 반환
 probe_only: 5xx crash</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>domain.invalid_base64
 domain.range_violation</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>semantic tag별 probe 1~3개 TC
 tag: base64_image, base64_template, score, user_id 등</t>
@@ -1069,10 +1021,9 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1110,20 +1061,15 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>invalid_enum</t>
+          <t>semantic_probe</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>semantic_probe</t>
+          <t>축 정의</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>축 정의</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>주요 Reason Code</t>
         </is>
@@ -1161,22 +1107,17 @@
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
           <t>must_fail
 query_param_invalid
 type_mismatch</t>
         </is>
       </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>파라미터의 타입·필수 여부·포맷이 API 스키마 명세에 적합한지 검증</t>
+        </is>
+      </c>
       <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>파라미터의 타입·필수 여부·포맷이 API 스키마 명세에 적합한지 검증</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>schema.missing_required
 schema.type_mismatch
@@ -1216,26 +1157,19 @@
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>must_fail
-enum_violation</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
           <t>must_fail / probe_only
 invalid_base64
 range_violation</t>
         </is>
       </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>값의 허용 범위, semantic 의미가 API 도메인 규칙에 맞는지 검증</t>
+        </is>
+      </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>값의 허용 범위, enum 목록, semantic 의미가 API 도메인 규칙에 맞는지 검증</t>
-        </is>
-      </c>
-      <c r="I4" s="10" t="inlineStr">
-        <is>
           <t>domain.range_violation
-domain.enum_violation
 domain.invalid_base64</t>
         </is>
       </c>
@@ -1275,15 +1209,10 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>서버가 요청을 처리할 수 있는 사전 조건(DB 데이터 존재 등) 충족 여부 검증</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>서버가 요청을 처리할 수 있는 사전 조건(DB 데이터 존재 등) 충족 여부 검증</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>state.precondition_not_met</t>
         </is>
@@ -1320,22 +1249,17 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>connection_refused→raise</t>
-        </is>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
           <t>probe_only 케이스
 status&lt;500 only
 (no crash)</t>
         </is>
       </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>예외적 입력·연결 오류에도 서버가 5xx crash 없이 응답하는지 검증</t>
+        </is>
+      </c>
       <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>예외적 입력·연결 오류에도 서버가 5xx crash 없이 응답하는지 검증</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>(crash 또는 connection_refused)</t>
         </is>
